--- a/data/trans_dic/Q45B_R-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/Q45B_R-Provincia-trans_dic.xlsx
@@ -524,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que han utilizado en los últimos 5 años cabinas o lámparas de rayos ultravioletas</t>
+          <t>Población que han utilizado en los últimos 5 años cabinas o lámparas de rayos ultravioletas (tasa de respuesta: 99,74%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -678,42 +678,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,92; 7,56</t>
+          <t>2,21; 7,7</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,28; 2,61</t>
+          <t>0,3; 2,92</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,64; 3,67</t>
+          <t>0,64; 3,92</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4,7; 11,73</t>
+          <t>4,79; 11,3</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>4,82; 11,28</t>
+          <t>5,02; 11,89</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,36; 6,28</t>
+          <t>1,49; 5,89</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,82; 8,1</t>
+          <t>3,88; 8,46</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2,83; 6,39</t>
+          <t>2,73; 6,43</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,91; 3,18</t>
+          <t>0,92; 3,22</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,56; 2,58</t>
+          <t>0,56; 2,64</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,41</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4,61; 8,92</t>
+          <t>4,42; 8,83</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,95; 5,36</t>
+          <t>1,89; 5,28</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,19; 1,61</t>
+          <t>0,19; 1,62</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,99; 5,6</t>
+          <t>2,97; 5,5</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,51; 3,37</t>
+          <t>1,52; 3,48</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,1; 0,88</t>
+          <t>0,1; 0,89</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,28</t>
+          <t>0,0; 2,14</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,29; 2,39</t>
+          <t>0,29; 2,4</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,82</t>
+          <t>0,0; 1,68</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5,64; 11,65</t>
+          <t>5,42; 11,83</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4,54; 9,98</t>
+          <t>4,39; 10,26</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,13; 9,06</t>
+          <t>4,22; 9,46</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,01; 6,38</t>
+          <t>3,15; 6,17</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2,67; 5,67</t>
+          <t>2,68; 5,63</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,35; 5,18</t>
+          <t>2,28; 4,92</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,76; 4,09</t>
+          <t>0,7; 4,01</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,2</t>
+          <t>0,0; 1,06</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,65</t>
+          <t>0,0; 1,86</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5,12; 10,72</t>
+          <t>5,1; 10,41</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2,22; 5,89</t>
+          <t>2,23; 5,9</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,19; 4,41</t>
+          <t>1,21; 4,43</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,39; 6,55</t>
+          <t>3,42; 6,5</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,15; 3,13</t>
+          <t>1,12; 3,21</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,76; 2,62</t>
+          <t>0,87; 2,53</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,86; 5,46</t>
+          <t>0,84; 5,61</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,73</t>
+          <t>0,0; 3,26</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,42; 3,81</t>
+          <t>0,42; 3,56</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4,44; 12,06</t>
+          <t>4,33; 12,44</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,24; 5,43</t>
+          <t>0,91; 5,32</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,38; 3,54</t>
+          <t>0,38; 3,13</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,03; 7,44</t>
+          <t>3,08; 7,83</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,89; 3,44</t>
+          <t>0,93; 3,53</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,42; 2,51</t>
+          <t>0,43; 2,77</t>
         </is>
       </c>
     </row>
@@ -1228,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,32</t>
+          <t>0,0; 1,77</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,73; 4,62</t>
+          <t>0,75; 4,33</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,36; 2,98</t>
+          <t>0,36; 2,97</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>8,76; 16,34</t>
+          <t>8,75; 16,1</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>3,51; 9,99</t>
+          <t>3,83; 9,64</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,33; 2,99</t>
+          <t>0,32; 2,67</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>4,24; 8,46</t>
+          <t>4,27; 8,59</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>2,63; 6,26</t>
+          <t>2,8; 6,32</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,49; 2,24</t>
+          <t>0,36; 2,28</t>
         </is>
       </c>
     </row>
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,28; 1,82</t>
+          <t>0,16; 1,84</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,23; 4,15</t>
+          <t>1,25; 4,05</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,34; 1,99</t>
+          <t>0,33; 2,07</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>7,04; 11,31</t>
+          <t>6,99; 11,61</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>6,9; 11,35</t>
+          <t>7,11; 11,53</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,76; 4,35</t>
+          <t>1,7; 4,32</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,84; 6,37</t>
+          <t>3,8; 6,24</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>4,56; 7,37</t>
+          <t>4,5; 7,2</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1,26; 2,81</t>
+          <t>1,31; 2,93</t>
         </is>
       </c>
     </row>
@@ -1448,47 +1448,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>2,36; 5,19</t>
+          <t>2,45; 5,18</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>4,45; 8,26</t>
+          <t>4,57; 8,19</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,88; 2,66</t>
+          <t>0,86; 2,54</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4,62; 8,06</t>
+          <t>4,7; 8,1</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>9,87; 14,64</t>
+          <t>10,03; 14,46</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>5,29; 8,66</t>
+          <t>5,24; 8,91</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,93; 6,27</t>
+          <t>4,03; 6,11</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>7,74; 10,77</t>
+          <t>7,62; 10,75</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>3,34; 5,42</t>
+          <t>3,41; 5,45</t>
         </is>
       </c>
     </row>
@@ -1558,47 +1558,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1,51; 2,53</t>
+          <t>1,52; 2,55</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1,99; 3,12</t>
+          <t>1,98; 3,14</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,64; 1,37</t>
+          <t>0,67; 1,33</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>6,92; 8,74</t>
+          <t>6,95; 8,83</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>6,52; 8,4</t>
+          <t>6,52; 8,35</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2,94; 4,13</t>
+          <t>2,98; 4,17</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>4,39; 5,53</t>
+          <t>4,44; 5,53</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>4,53; 5,59</t>
+          <t>4,49; 5,58</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1,93; 2,65</t>
+          <t>1,95; 2,64</t>
         </is>
       </c>
     </row>
@@ -1654,7 +1654,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que han utilizado en los últimos 5 años cabinas o lámparas de rayos ultravioletas</t>
+          <t>Población que han utilizado en los últimos 5 años cabinas o lámparas de rayos ultravioletas (tasa de respuesta: 99,74%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1861,47 +1861,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>5238; 20627</t>
+          <t>6029; 21014</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>837; 7702</t>
+          <t>880; 8620</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1846; 10603</t>
+          <t>1861; 11342</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>12263; 30609</t>
+          <t>12496; 29467</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>13858; 32407</t>
+          <t>14420; 34164</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3929; 18140</t>
+          <t>4307; 17017</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>20418; 43243</t>
+          <t>20713; 45144</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>16467; 37210</t>
+          <t>15916; 37438</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>7531; 22632</t>
+          <t>7501; 22658</t>
         </is>
       </c>
     </row>
@@ -2024,47 +2024,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4468; 15686</t>
+          <t>4522; 15873</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2852; 13067</t>
+          <t>2831; 13365</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 2027</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>23223; 44969</t>
+          <t>22298; 44503</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>10192; 28029</t>
+          <t>9900; 27626</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>980; 8416</t>
+          <t>974; 8497</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>29802; 55853</t>
+          <t>29610; 54800</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>15502; 34652</t>
+          <t>15583; 35810</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>980; 8980</t>
+          <t>979; 9108</t>
         </is>
       </c>
     </row>
@@ -2187,47 +2187,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 7284</t>
+          <t>0; 6824</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>926; 7720</t>
+          <t>930; 7740</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 5795</t>
+          <t>0; 5337</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>18902; 39082</t>
+          <t>18180; 39696</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>15444; 33927</t>
+          <t>14945; 34901</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>13741; 30113</t>
+          <t>14020; 31435</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>19664; 41747</t>
+          <t>20640; 40388</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>17714; 37627</t>
+          <t>17769; 37314</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>15305; 33652</t>
+          <t>14791; 32006</t>
         </is>
       </c>
     </row>
@@ -2350,47 +2350,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2727; 14676</t>
+          <t>2513; 14372</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 4478</t>
+          <t>0; 3926</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 6089</t>
+          <t>0; 6857</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>19021; 39838</t>
+          <t>18943; 38682</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>8604; 22850</t>
+          <t>8631; 22871</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>4613; 17016</t>
+          <t>4655; 17126</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>24729; 47825</t>
+          <t>24956; 47440</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>8750; 23809</t>
+          <t>8492; 24371</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>5719; 19736</t>
+          <t>6532; 19105</t>
         </is>
       </c>
     </row>
@@ -2513,47 +2513,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>1742; 11096</t>
+          <t>1716; 11414</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 7892</t>
+          <t>0; 6891</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>881; 8038</t>
+          <t>894; 7523</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>9225; 25040</t>
+          <t>8991; 25841</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>2715; 11872</t>
+          <t>1994; 11635</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>821; 7719</t>
+          <t>826; 6819</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>12469; 30568</t>
+          <t>12643; 32183</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>3837; 14782</t>
+          <t>4008; 15164</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>1805; 10788</t>
+          <t>1860; 11888</t>
         </is>
       </c>
     </row>
@@ -2676,47 +2676,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 3588</t>
+          <t>0; 4782</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1984; 12621</t>
+          <t>2052; 11825</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>943; 7845</t>
+          <t>947; 7802</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>24355; 45461</t>
+          <t>24341; 44785</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>9769; 27785</t>
+          <t>10651; 26825</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>886; 8128</t>
+          <t>878; 7256</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>23250; 46447</t>
+          <t>23448; 47173</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>14476; 34475</t>
+          <t>15421; 34822</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>2602; 11970</t>
+          <t>1913; 12213</t>
         </is>
       </c>
     </row>
@@ -2839,47 +2839,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>1729; 11197</t>
+          <t>1005; 11308</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>8048; 27223</t>
+          <t>8204; 26577</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>2197; 12985</t>
+          <t>2182; 13486</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>44932; 72196</t>
+          <t>44593; 74098</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>47726; 78472</t>
+          <t>49180; 79727</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>12081; 29852</t>
+          <t>11693; 29662</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>48116; 79854</t>
+          <t>47599; 78233</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>61413; 99297</t>
+          <t>60692; 97012</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>16925; 37636</t>
+          <t>17470; 39242</t>
         </is>
       </c>
     </row>
@@ -3002,47 +3002,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>17574; 38594</t>
+          <t>18191; 38528</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>34584; 64257</t>
+          <t>35557; 63709</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>6821; 20685</t>
+          <t>6658; 19773</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>36197; 63159</t>
+          <t>36799; 63437</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>80817; 119844</t>
+          <t>82107; 118399</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>43631; 71457</t>
+          <t>43201; 73519</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>60052; 95766</t>
+          <t>61537; 93292</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>123587; 171958</t>
+          <t>121695; 171581</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>53568; 86820</t>
+          <t>54575; 87275</t>
         </is>
       </c>
     </row>
@@ -3165,47 +3165,47 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>49328; 82988</t>
+          <t>49932; 83563</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>67959; 106551</t>
+          <t>67604; 107270</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>21737; 46443</t>
+          <t>22738; 44824</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>233817; 295437</t>
+          <t>234755; 298441</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>231049; 297812</t>
+          <t>231100; 295831</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>103962; 145822</t>
+          <t>105302; 147208</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>292503; 368021</t>
+          <t>295689; 368387</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>315059; 389265</t>
+          <t>312254; 388136</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>133144; 182921</t>
+          <t>134776; 182516</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/Q45B_R-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/Q45B_R-Provincia-trans_dic.xlsx
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,21; 7,7</t>
+          <t>1,9; 7,49</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,3; 2,92</t>
+          <t>0,3; 2,8</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,64; 3,92</t>
+          <t>0,65; 3,68</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4,79; 11,3</t>
+          <t>4,8; 11,5</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>5,02; 11,89</t>
+          <t>4,63; 11,98</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,49; 5,89</t>
+          <t>1,5; 6,28</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,88; 8,46</t>
+          <t>4,03; 7,94</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2,73; 6,43</t>
+          <t>2,89; 6,67</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,3; 3,92</t>
+          <t>1,28; 4,06</t>
         </is>
       </c>
     </row>
@@ -788,12 +788,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,92; 3,22</t>
+          <t>0,82; 3,26</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,56; 2,64</t>
+          <t>0,56; 2,69</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -803,32 +803,32 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4,42; 8,83</t>
+          <t>4,5; 8,8</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,89; 5,28</t>
+          <t>1,92; 5,2</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,19; 1,62</t>
+          <t>0,19; 1,63</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,97; 5,5</t>
+          <t>2,95; 5,62</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,52; 3,48</t>
+          <t>1,45; 3,26</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,1; 0,89</t>
+          <t>0,1; 0,82</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,14</t>
+          <t>0,0; 1,8</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,29; 2,4</t>
+          <t>0,29; 2,73</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,68</t>
+          <t>0,0; 1,57</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5,42; 11,83</t>
+          <t>5,68; 12,22</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4,39; 10,26</t>
+          <t>4,58; 10,11</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,22; 9,46</t>
+          <t>4,18; 9,24</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,15; 6,17</t>
+          <t>3,18; 6,4</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2,68; 5,63</t>
+          <t>2,72; 5,54</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,28; 4,92</t>
+          <t>2,28; 4,99</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,7; 4,01</t>
+          <t>0,82; 3,98</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,06</t>
+          <t>0,0; 1,18</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,86</t>
+          <t>0,0; 1,89</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5,1; 10,41</t>
+          <t>5,14; 10,6</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2,23; 5,9</t>
+          <t>2,2; 5,8</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,21; 4,43</t>
+          <t>1,21; 4,47</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,42; 6,5</t>
+          <t>3,34; 6,62</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,12; 3,21</t>
+          <t>1,15; 3,13</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,87; 2,53</t>
+          <t>0,81; 2,65</t>
         </is>
       </c>
     </row>
@@ -1118,22 +1118,22 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,84; 5,61</t>
+          <t>0,88; 5,85</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,26</t>
+          <t>0,0; 3,28</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,42; 3,56</t>
+          <t>0,42; 4,13</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4,33; 12,44</t>
+          <t>4,4; 12,58</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1143,22 +1143,22 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,38; 3,13</t>
+          <t>0,0; 3,12</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,08; 7,83</t>
+          <t>3,24; 7,93</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,93; 3,53</t>
+          <t>0,88; 3,58</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,43; 2,77</t>
+          <t>0,42; 2,59</t>
         </is>
       </c>
     </row>
@@ -1228,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,77</t>
+          <t>0,0; 1,32</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,75; 4,33</t>
+          <t>0,75; 4,34</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,36; 2,97</t>
+          <t>0,36; 3,27</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>8,75; 16,1</t>
+          <t>8,48; 16,54</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>3,83; 9,64</t>
+          <t>3,73; 9,81</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,32; 2,67</t>
+          <t>0,33; 2,88</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>4,27; 8,59</t>
+          <t>4,31; 8,77</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>2,8; 6,32</t>
+          <t>2,78; 6,33</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,36; 2,28</t>
+          <t>0,5; 2,13</t>
         </is>
       </c>
     </row>
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,16; 1,84</t>
+          <t>0,28; 1,86</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,25; 4,05</t>
+          <t>1,26; 4,05</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,33; 2,07</t>
+          <t>0,34; 2,16</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>6,99; 11,61</t>
+          <t>6,82; 11,2</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>7,11; 11,53</t>
+          <t>7,11; 11,77</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,7; 4,32</t>
+          <t>1,78; 4,44</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,8; 6,24</t>
+          <t>3,87; 6,4</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>4,5; 7,2</t>
+          <t>4,65; 7,23</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1,31; 2,93</t>
+          <t>1,29; 2,8</t>
         </is>
       </c>
     </row>
@@ -1448,47 +1448,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>2,45; 5,18</t>
+          <t>2,36; 5,19</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>4,57; 8,19</t>
+          <t>4,5; 8,0</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,86; 2,54</t>
+          <t>0,86; 2,56</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4,7; 8,1</t>
+          <t>4,67; 8,17</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>10,03; 14,46</t>
+          <t>9,96; 14,7</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>5,24; 8,91</t>
+          <t>5,37; 8,88</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,03; 6,11</t>
+          <t>3,94; 6,08</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>7,62; 10,75</t>
+          <t>7,95; 10,97</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>3,41; 5,45</t>
+          <t>3,38; 5,43</t>
         </is>
       </c>
     </row>
@@ -1558,47 +1558,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1,52; 2,55</t>
+          <t>1,52; 2,51</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1,98; 3,14</t>
+          <t>2,04; 3,12</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,67; 1,33</t>
+          <t>0,66; 1,27</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>6,95; 8,83</t>
+          <t>6,94; 8,87</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>6,52; 8,35</t>
+          <t>6,55; 8,33</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2,98; 4,17</t>
+          <t>2,98; 4,14</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>4,44; 5,53</t>
+          <t>4,39; 5,43</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>4,49; 5,58</t>
+          <t>4,52; 5,58</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1,95; 2,64</t>
+          <t>1,93; 2,63</t>
         </is>
       </c>
     </row>
@@ -1861,47 +1861,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>6029; 21014</t>
+          <t>5180; 20438</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>880; 8620</t>
+          <t>871; 8251</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1861; 11342</t>
+          <t>1871; 10648</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>12496; 29467</t>
+          <t>12526; 30008</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>14420; 34164</t>
+          <t>13287; 34408</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>4307; 17017</t>
+          <t>4342; 18119</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>20713; 45144</t>
+          <t>21509; 42412</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>15916; 37438</t>
+          <t>16830; 38827</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>7501; 22658</t>
+          <t>7408; 23450</t>
         </is>
       </c>
     </row>
@@ -2024,12 +2024,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4522; 15873</t>
+          <t>4020; 16059</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2831; 13365</t>
+          <t>2841; 13601</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -2039,32 +2039,32 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>22298; 44503</t>
+          <t>22700; 44344</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>9900; 27626</t>
+          <t>10059; 27157</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>974; 8497</t>
+          <t>978; 8506</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>29610; 54800</t>
+          <t>29445; 56053</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>15583; 35810</t>
+          <t>14885; 33543</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>979; 9108</t>
+          <t>980; 8385</t>
         </is>
       </c>
     </row>
@@ -2187,47 +2187,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 6824</t>
+          <t>0; 5734</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>930; 7740</t>
+          <t>929; 8814</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 5337</t>
+          <t>0; 4984</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>18180; 39696</t>
+          <t>19043; 40998</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>14945; 34901</t>
+          <t>15560; 34389</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>14020; 31435</t>
+          <t>13886; 30720</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>20640; 40388</t>
+          <t>20792; 41878</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>17769; 37314</t>
+          <t>18060; 36761</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>14791; 32006</t>
+          <t>14827; 32450</t>
         </is>
       </c>
     </row>
@@ -2350,47 +2350,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2513; 14372</t>
+          <t>2958; 14285</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 3926</t>
+          <t>0; 4395</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 6857</t>
+          <t>0; 6962</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>18943; 38682</t>
+          <t>19104; 39356</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>8631; 22871</t>
+          <t>8536; 22501</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>4655; 17126</t>
+          <t>4675; 17265</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>24956; 47440</t>
+          <t>24416; 48347</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>8492; 24371</t>
+          <t>8754; 23769</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>6532; 19105</t>
+          <t>6085; 19955</t>
         </is>
       </c>
     </row>
@@ -2513,47 +2513,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>1716; 11414</t>
+          <t>1786; 11887</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 6891</t>
+          <t>0; 6946</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>894; 7523</t>
+          <t>880; 8715</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>8991; 25841</t>
+          <t>9133; 26116</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>1994; 11635</t>
+          <t>1983; 11634</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>826; 6819</t>
+          <t>0; 6796</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>12643; 32183</t>
+          <t>13321; 32602</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>4008; 15164</t>
+          <t>3787; 15419</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>1860; 11888</t>
+          <t>1818; 11111</t>
         </is>
       </c>
     </row>
@@ -2676,47 +2676,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 4782</t>
+          <t>0; 3584</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2052; 11825</t>
+          <t>2046; 11853</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>947; 7802</t>
+          <t>951; 8603</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>24341; 44785</t>
+          <t>23597; 46011</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>10651; 26825</t>
+          <t>10386; 27290</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>878; 7256</t>
+          <t>893; 7828</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>23448; 47173</t>
+          <t>23663; 48152</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>15421; 34822</t>
+          <t>15305; 34911</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1913; 12213</t>
+          <t>2700; 11391</t>
         </is>
       </c>
     </row>
@@ -2839,47 +2839,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>1005; 11308</t>
+          <t>1697; 11443</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>8204; 26577</t>
+          <t>8264; 26593</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>2182; 13486</t>
+          <t>2233; 14111</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>44593; 74098</t>
+          <t>43515; 71462</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>49180; 79727</t>
+          <t>49186; 81391</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>11693; 29662</t>
+          <t>12226; 30492</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>47599; 78233</t>
+          <t>48544; 80149</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>60692; 97012</t>
+          <t>62722; 97489</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>17470; 39242</t>
+          <t>17240; 37434</t>
         </is>
       </c>
     </row>
@@ -3002,47 +3002,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>18191; 38528</t>
+          <t>17561; 38575</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>35557; 63709</t>
+          <t>35028; 62276</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>6658; 19773</t>
+          <t>6720; 19880</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>36799; 63437</t>
+          <t>36552; 64046</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>82107; 118399</t>
+          <t>81489; 120308</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>43201; 73519</t>
+          <t>44287; 73286</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>61537; 93292</t>
+          <t>60184; 92923</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>121695; 171581</t>
+          <t>126867; 175202</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>54575; 87275</t>
+          <t>54236; 87034</t>
         </is>
       </c>
     </row>
@@ -3165,47 +3165,47 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>49932; 83563</t>
+          <t>49774; 82123</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>67604; 107270</t>
+          <t>69767; 106528</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>22738; 44824</t>
+          <t>22425; 43031</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>234755; 298441</t>
+          <t>234665; 299743</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>231100; 295831</t>
+          <t>232067; 295192</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>105302; 147208</t>
+          <t>105092; 146124</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>295689; 368387</t>
+          <t>291859; 361735</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>312254; 388136</t>
+          <t>314296; 388280</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>134776; 182516</t>
+          <t>133241; 182052</t>
         </is>
       </c>
     </row>
